--- a/apps/mobile/www/assets/Modelo_Importacao_SmartFarm.xlsx
+++ b/apps/mobile/www/assets/Modelo_Importacao_SmartFarm.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LEIA-ME" sheetId="1" r:id="Recffc2bd115f4f72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Propriedades" sheetId="2" r:id="R9b37d6a4ff974147"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Talhoes" sheetId="3" r:id="R46c7960e84ae4490"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produtos" sheetId="4" r:id="R5e9f17b09ef449f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LEIA-ME" sheetId="1" r:id="R0b0d1e38eedb445d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Propriedades" sheetId="2" r:id="Rb0187e88e98c4ce0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Talhoes" sheetId="3" r:id="R2ed0868bfd124f95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Produtos" sheetId="4" r:id="R8a3fd8b8937d4826"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2215,7 +2215,7 @@
     <x:col min="2" max="2" width="21" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="21" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="17" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="17" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="23" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="17" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="17" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="17" hidden="0" customWidth="1"/>
@@ -2229,7 +2229,7 @@
     </x:row>
     <x:row r="2" ht="34" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>Obrigatórios: Produtor, Propriedade e Talhão. Área deve ser informada em hectares. O aplicativo ordenará 3.1, 3.2, 3.3 numericamente.</x:v>
+        <x:v>Obrigatórios: Produtor, Propriedade e Talhão. Informe a área em hectares e a quantidade de pés de café de cada talhão. O aplicativo ordenará 3.1, 3.2, 3.3 numericamente.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="30" customHeight="1">
@@ -2246,7 +2246,7 @@
         <x:v>Área (ha)</x:v>
       </x:c>
       <x:c r="E4" s="28" t="str">
-        <x:v>Nº de plantas</x:v>
+        <x:v>Quantidade de pés de café</x:v>
       </x:c>
       <x:c r="F4" s="28" t="str">
         <x:v>Espaçamento entre linhas (m)</x:v>
